--- a/data/single_run/input/components/c2/c2_meisner.xlsx
+++ b/data/single_run/input/components/c2/c2_meisner.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ccp_1,ccp_2,ccp_3,ccp_4,ccp_5,ccp_6,ccp_7,ccp_8,ccp_9,ccp_10,ccp_11,ccp_12,ccp_13,ccp_14,ccp_15</t>
+          <t>ccp_1,ccp_2,ccp_3,ccp_4,ccp_5,ccp_6,ccp_7,ccp_8,ccp_9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AMB001,AMB002,AMB003,AMB004,AMB005,AMB006,AMB007,AMB008,AMB009,AMB010,AMB011,AMB012,AMB013,AMB014,AMB015,AMB016,AMB017,AMB018,AMB019,AMB020,AMB021,AMB022,AMB023,AMB024,AMB025,AMB026,AMB027,AMB028,AMB029,AMB030,AMB031,AMB032,AMB033,AMB034,AMB035,AMB036,AMB037,AMB038,AMB039,AMB040,AMB041,AMB042,AMB043,AMB044,AMB045</t>
+          <t>AMB001,AMB002,AMB003,AMB004,AMB005,AMB006,AMB007,AMB008,AMB009,AMB010,AMB011,AMB012,AMB013,AMB014,AMB015,AMB016,AMB017,AMB018,AMB019,AMB020,AMB021,AMB022,AMB023,AMB024,AMB025,AMB026,AMB027</t>
         </is>
       </c>
     </row>
@@ -458,12 +458,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>r1_1,r1_2,r1_3,r1_4,r1_5,r1_6,r1_7,r1_8,r1_9,r1_10,r1_11,r1_12,r1_13,r1_14,r1_15</t>
+          <t>r1_1,r1_2,r1_3,r1_4,r1_5,r1_6,r1_7,r1_8,r1_9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AMB046,AMB047,AMB048,AMB049,AMB050,AMB051,AMB052,AMB053,AMB054,AMB055,AMB056,AMB057</t>
+          <t>AMB028,AMB029,AMB030,AMB031,AMB032,AMB033,AMB034,AMB035,AMB036,AMB037,AMB038,AMB039</t>
         </is>
       </c>
     </row>
